--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED53741A-60A6-49A5-AA05-32C4721F665F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF86FD0-386E-4B55-BBCD-48705E818094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>CEDULA</t>
   </si>
@@ -144,72 +144,6 @@
   </si>
   <si>
     <t>BRYAN ALEJANDRO SANCHEZ GARCIA</t>
-  </si>
-  <si>
-    <t>1,000,000 VALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213,889 VALES </t>
-  </si>
-  <si>
-    <t>450,000 VALES</t>
-  </si>
-  <si>
-    <t>300,000 VALES</t>
-  </si>
-  <si>
-    <t>392,854 VALES</t>
-  </si>
-  <si>
-    <t>1 DIA VAC+7,000 CARITAS+57,822 VALES</t>
-  </si>
-  <si>
-    <t>210,089 CARITAS + 5,042 UTILIDADES + 16,000 SUGERIDOS+57,257 COMISION + 200,000 VALES</t>
-  </si>
-  <si>
-    <t>16,000 SUGERIDOS</t>
-  </si>
-  <si>
-    <t>1 DIA LCR + 36,000 SUGERIDOS + 7,000 CARITAS+ 15,000 VALE</t>
-  </si>
-  <si>
-    <t>1 DIA LNCR + 7,000 CARITAS</t>
-  </si>
-  <si>
-    <t>35,000 CARITAS</t>
-  </si>
-  <si>
-    <t>28,000 CARITAS</t>
-  </si>
-  <si>
-    <t>1 DIA LCNR+9,992 DOMINICAL+281,155 VALES</t>
-  </si>
-  <si>
-    <t>1 DIA LCNR+9,992 DOMINICAL + 28,000 CARITAS+75,000 VALES</t>
-  </si>
-  <si>
-    <t>1 DIA LCR +1 DIA LCNR + PAGO EL 1/07/2026</t>
-  </si>
-  <si>
-    <t>151,726 CARITAS + 1 DIA LCL</t>
-  </si>
-  <si>
-    <t>INGRESA 23 JUN+150,000 VALES</t>
-  </si>
-  <si>
-    <t>18,583 UTILIDADES + 18,000 SUGERIDOS + 21,000 CARITAS</t>
-  </si>
-  <si>
-    <t>35,938 UTILIDADES + 12,000 SUGERIDOS + 35,000 CARITAS</t>
-  </si>
-  <si>
-    <t>151,726 CARITAS</t>
-  </si>
-  <si>
-    <t>54,059 UTILIDADES + 20,000 SUGERIDOS + 49,000 CARITAS</t>
-  </si>
-  <si>
-    <t>14,000 CARITAS</t>
   </si>
 </sst>
 </file>
@@ -838,9 +772,7 @@
       <c r="H2" s="13">
         <v>1000000</v>
       </c>
-      <c r="I2" s="20" t="s">
-        <v>36</v>
-      </c>
+      <c r="I2" s="20"/>
       <c r="J2" s="13">
         <f>+C2+D2+E2-F2+G2-H2</f>
         <v>2360000.0000000005</v>
@@ -863,7 +795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>94288721</v>
       </c>
@@ -888,9 +820,7 @@
       <c r="H3" s="13">
         <v>213889</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>37</v>
-      </c>
+      <c r="I3" s="21"/>
       <c r="J3" s="13">
         <f t="shared" ref="J3:J19" si="0">+C3+D3+E3-F3+G3-H3</f>
         <v>1346038.6</v>
@@ -907,15 +837,13 @@
       <c r="N3" s="14">
         <v>36583</v>
       </c>
-      <c r="O3" s="22" t="s">
-        <v>53</v>
-      </c>
+      <c r="O3" s="22"/>
       <c r="P3" s="14">
         <f>L3-M3-N3</f>
         <v>944807</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1001200622</v>
       </c>
@@ -940,9 +868,7 @@
       <c r="H4" s="13">
         <v>450000</v>
       </c>
-      <c r="I4" s="22" t="s">
-        <v>38</v>
-      </c>
+      <c r="I4" s="22"/>
       <c r="J4" s="13">
         <f t="shared" si="0"/>
         <v>1009927.6000000001</v>
@@ -959,9 +885,7 @@
       <c r="N4" s="14">
         <v>47938</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>54</v>
-      </c>
+      <c r="O4" s="25"/>
       <c r="P4" s="14">
         <f t="shared" ref="P4:P20" si="1">L4-M4-N4</f>
         <v>548462</v>
@@ -992,9 +916,7 @@
       <c r="H5" s="13">
         <v>300000</v>
       </c>
-      <c r="I5" s="21" t="s">
-        <v>39</v>
-      </c>
+      <c r="I5" s="21"/>
       <c r="J5" s="13">
         <f t="shared" si="0"/>
         <v>1259927.6000000001</v>
@@ -1011,15 +933,13 @@
       <c r="N5" s="14">
         <v>0</v>
       </c>
-      <c r="O5" s="22" t="s">
-        <v>55</v>
-      </c>
+      <c r="O5" s="22"/>
       <c r="P5" s="14">
         <f t="shared" si="1"/>
         <v>439022</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>80875830</v>
       </c>
@@ -1044,9 +964,7 @@
       <c r="H6" s="13">
         <v>392854</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>40</v>
-      </c>
+      <c r="I6" s="23"/>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
         <v>1171742.68</v>
@@ -1063,9 +981,7 @@
       <c r="N6" s="14">
         <v>74059</v>
       </c>
-      <c r="O6" s="22" t="s">
-        <v>56</v>
-      </c>
+      <c r="O6" s="22"/>
       <c r="P6" s="14">
         <f t="shared" si="1"/>
         <v>1409013</v>
@@ -1096,9 +1012,7 @@
       <c r="H7" s="13">
         <v>64822</v>
       </c>
-      <c r="I7" s="21" t="s">
-        <v>41</v>
-      </c>
+      <c r="I7" s="21"/>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
         <v>837777.09333333338</v>
@@ -1121,7 +1035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1193092448</v>
       </c>
@@ -1146,9 +1060,7 @@
       <c r="H8" s="13">
         <v>488388</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>42</v>
-      </c>
+      <c r="I8" s="24"/>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
         <v>1071539.6000000001</v>
@@ -1196,9 +1108,7 @@
       <c r="H9" s="13">
         <v>16000</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>43</v>
-      </c>
+      <c r="I9" s="22"/>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
         <v>1143927.6000000001</v>
@@ -1215,9 +1125,7 @@
       <c r="N9" s="14">
         <v>0</v>
       </c>
-      <c r="O9" s="22" t="s">
-        <v>57</v>
-      </c>
+      <c r="O9" s="22"/>
       <c r="P9" s="14">
         <f t="shared" si="1"/>
         <v>12404</v>
@@ -1248,9 +1156,7 @@
       <c r="H10" s="13">
         <v>58000</v>
       </c>
-      <c r="I10" s="21" t="s">
-        <v>44</v>
-      </c>
+      <c r="I10" s="21"/>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
         <v>812300.75333333341</v>
@@ -1394,9 +1300,7 @@
       <c r="H13" s="13">
         <v>7000</v>
       </c>
-      <c r="I13" s="20" t="s">
-        <v>45</v>
-      </c>
+      <c r="I13" s="20"/>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
         <v>890930.01333333342</v>
@@ -1492,9 +1396,7 @@
       <c r="H15" s="13">
         <v>35000</v>
       </c>
-      <c r="I15" s="22" t="s">
-        <v>46</v>
-      </c>
+      <c r="I15" s="22"/>
       <c r="J15" s="13">
         <f t="shared" si="0"/>
         <v>824927.6</v>
@@ -1542,9 +1444,7 @@
       <c r="H16" s="13">
         <v>28000</v>
       </c>
-      <c r="I16" s="22" t="s">
-        <v>47</v>
-      </c>
+      <c r="I16" s="22"/>
       <c r="J16" s="13">
         <f t="shared" si="0"/>
         <v>1228470.6000000001</v>
@@ -1592,9 +1492,7 @@
       <c r="H17" s="13">
         <v>291147</v>
       </c>
-      <c r="I17" s="22" t="s">
-        <v>48</v>
-      </c>
+      <c r="I17" s="22"/>
       <c r="J17" s="13">
         <f t="shared" si="0"/>
         <v>843904.01333333342</v>
@@ -1642,9 +1540,7 @@
       <c r="H18" s="13">
         <v>112992</v>
       </c>
-      <c r="I18" s="22" t="s">
-        <v>49</v>
-      </c>
+      <c r="I18" s="22"/>
       <c r="J18" s="13">
         <f t="shared" si="0"/>
         <v>684938.01333333342</v>
@@ -1692,9 +1588,7 @@
       <c r="H19" s="13">
         <v>0</v>
       </c>
-      <c r="I19" s="22" t="s">
-        <v>50</v>
-      </c>
+      <c r="I19" s="22"/>
       <c r="J19" s="13">
         <f t="shared" si="0"/>
         <v>1159655.4333333336</v>
@@ -1742,9 +1636,7 @@
       <c r="H20" s="13">
         <v>151729</v>
       </c>
-      <c r="I20" s="22" t="s">
-        <v>51</v>
-      </c>
+      <c r="I20" s="22"/>
       <c r="J20" s="13">
         <f>+C20+D20+E20-F20+G20-H20</f>
         <v>1061183.4333333336</v>
@@ -1792,9 +1684,7 @@
       <c r="H21" s="13">
         <v>150000</v>
       </c>
-      <c r="I21" s="22" t="s">
-        <v>52</v>
-      </c>
+      <c r="I21" s="22"/>
       <c r="J21" s="13">
         <f>+C21+D21+E21-F21+G21-H21</f>
         <v>345980.69333333336</v>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF86FD0-386E-4B55-BBCD-48705E818094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC95C74-773B-4FC4-B0DA-93BA29213C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -835,12 +835,12 @@
         <v>21000</v>
       </c>
       <c r="N3" s="14">
-        <v>36583</v>
+        <v>0</v>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="14">
         <f>L3-M3-N3</f>
-        <v>944807</v>
+        <v>981390</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -883,12 +883,12 @@
         <v>35000</v>
       </c>
       <c r="N4" s="14">
-        <v>47938</v>
+        <v>0</v>
       </c>
       <c r="O4" s="25"/>
       <c r="P4" s="14">
         <f t="shared" ref="P4:P20" si="1">L4-M4-N4</f>
-        <v>548462</v>
+        <v>596400</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -979,12 +979,12 @@
         <v>49000</v>
       </c>
       <c r="N6" s="14">
-        <v>74059</v>
+        <v>0</v>
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="14">
         <f t="shared" si="1"/>
-        <v>1409013</v>
+        <v>1483072</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC95C74-773B-4FC4-B0DA-93BA29213C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B508FB93-948B-463C-8B20-984BD555719A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -781,6 +781,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="13">
+        <f>K2-G2</f>
         <v>0</v>
       </c>
       <c r="M2" s="13">
@@ -829,6 +830,7 @@
         <v>1702390</v>
       </c>
       <c r="L3" s="13">
+        <f t="shared" ref="L3:L21" si="1">K3-G3</f>
         <v>1002390</v>
       </c>
       <c r="M3" s="13">
@@ -877,6 +879,7 @@
         <v>1231400</v>
       </c>
       <c r="L4" s="13">
+        <f t="shared" si="1"/>
         <v>631400</v>
       </c>
       <c r="M4" s="13">
@@ -887,7 +890,7 @@
       </c>
       <c r="O4" s="25"/>
       <c r="P4" s="14">
-        <f t="shared" ref="P4:P20" si="1">L4-M4-N4</f>
+        <f t="shared" ref="P4:P20" si="2">L4-M4-N4</f>
         <v>596400</v>
       </c>
     </row>
@@ -925,6 +928,7 @@
         <v>1290748</v>
       </c>
       <c r="L5" s="13">
+        <f t="shared" si="1"/>
         <v>590748</v>
       </c>
       <c r="M5" s="13">
@@ -935,7 +939,7 @@
       </c>
       <c r="O5" s="22"/>
       <c r="P5" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>439022</v>
       </c>
     </row>
@@ -973,6 +977,7 @@
         <v>2232072</v>
       </c>
       <c r="L6" s="13">
+        <f t="shared" si="1"/>
         <v>1532072</v>
       </c>
       <c r="M6" s="13">
@@ -983,7 +988,7 @@
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1483072</v>
       </c>
     </row>
@@ -1021,7 +1026,8 @@
         <v>0</v>
       </c>
       <c r="L7" s="13">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>-100000</v>
       </c>
       <c r="M7" s="13">
         <v>0</v>
@@ -1031,8 +1037,8 @@
       </c>
       <c r="O7" s="23"/>
       <c r="P7" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-100000</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1069,7 +1075,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="13">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>-700000</v>
       </c>
       <c r="M8" s="13">
         <v>0</v>
@@ -1080,7 +1087,7 @@
       <c r="O8" s="25"/>
       <c r="P8" s="14">
         <f>L8-M8-N8</f>
-        <v>0</v>
+        <v>-700000</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1117,6 +1124,7 @@
         <v>326404</v>
       </c>
       <c r="L9" s="13">
+        <f t="shared" si="1"/>
         <v>26404</v>
       </c>
       <c r="M9" s="13">
@@ -1127,7 +1135,7 @@
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12404</v>
       </c>
     </row>
@@ -1175,7 +1183,7 @@
       </c>
       <c r="O10" s="22"/>
       <c r="P10" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1223,7 +1231,7 @@
       </c>
       <c r="O11" s="23"/>
       <c r="P11" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1261,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="13">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
@@ -1271,8 +1279,8 @@
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="14">
-        <f t="shared" si="1"/>
-        <v>572000</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1319,7 +1327,7 @@
       </c>
       <c r="O13" s="23"/>
       <c r="P13" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1367,7 +1375,7 @@
       </c>
       <c r="O14" s="23"/>
       <c r="P14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1415,7 +1423,7 @@
       </c>
       <c r="O15" s="23"/>
       <c r="P15" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1463,7 +1471,7 @@
       </c>
       <c r="O16" s="23"/>
       <c r="P16" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1511,7 +1519,7 @@
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1559,7 +1567,7 @@
       </c>
       <c r="O18" s="23"/>
       <c r="P18" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1597,6 +1605,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M19" s="13">
@@ -1607,7 +1616,7 @@
       </c>
       <c r="O19" s="23"/>
       <c r="P19" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1645,6 +1654,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M20" s="13">
@@ -1655,7 +1665,7 @@
       </c>
       <c r="O20" s="23"/>
       <c r="P20" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1693,6 +1703,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M21" s="13">

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B508FB93-948B-463C-8B20-984BD555719A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A793A8E8-D629-4D33-B413-D9A6A9790CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -156,7 +156,7 @@
     <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +197,14 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u val="singleAccounting"/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Century Gothic"/>
@@ -261,7 +269,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -337,6 +345,9 @@
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1235,7 +1246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>79593400</v>
       </c>
@@ -1260,7 +1271,7 @@
       <c r="H12" s="13">
         <v>0</v>
       </c>
-      <c r="I12" s="20"/>
+      <c r="I12" s="26"/>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
         <v>8578000</v>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A793A8E8-D629-4D33-B413-D9A6A9790CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9884A3-91E5-48CA-925A-244D94946A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>CEDULA</t>
   </si>
@@ -128,9 +117,6 @@
     <t>TOVAR AREVALO JULIAN GIOVANNI</t>
   </si>
   <si>
-    <t>HERRERA NINCO JUAN SEBASTIAN</t>
-  </si>
-  <si>
     <t>DIONISIO NAVARRETE JOHAN ANDREY</t>
   </si>
   <si>
@@ -144,6 +130,54 @@
   </si>
   <si>
     <t>BRYAN ALEJANDRO SANCHEZ GARCIA</t>
+  </si>
+  <si>
+    <t>3 DIAS VACACIONES</t>
+  </si>
+  <si>
+    <t>7,000 1 CARITA</t>
+  </si>
+  <si>
+    <t>21,000 3 CARITAS+20,000 SUGERIDOS+22,672  EXCENDE BONO</t>
+  </si>
+  <si>
+    <t>1 DIA LCNR+7,000 1 CARITA+22,000 SUGERIDOS+27,000 VALES</t>
+  </si>
+  <si>
+    <t>14,000 2 CARITAS</t>
+  </si>
+  <si>
+    <t>28,000 4 CARITAS</t>
+  </si>
+  <si>
+    <t>49,000 7 CARITAS</t>
+  </si>
+  <si>
+    <t>28,000 4 CARITAS+22,000 SUGERIDOS</t>
+  </si>
+  <si>
+    <t>1 DIA LCNR+ 58,363 (1 DIAS)+63,000 9 CARITAS+9996 Dominical</t>
+  </si>
+  <si>
+    <t>28,000 4 CARITAS+10,000 VALES+50,000 VALES</t>
+  </si>
+  <si>
+    <t>42,000 6 CARITAS+6,391 UTILIDADES+10,000 SUGERIDO+682,826 VALES</t>
+  </si>
+  <si>
+    <t>10,000 DOTACION+56,000 8 CARITAS+119,810 UTILIDADES+22,000 SUGERIDOS+449,463 VALES</t>
+  </si>
+  <si>
+    <t>58,363 (1 DIAS)+  98,000 14 CARITAS+101,305 VALES</t>
+  </si>
+  <si>
+    <t>42,000 6 CARITAS+20,722 UTILIDADES+48,000 SUGERIDO+400,000 VALES</t>
+  </si>
+  <si>
+    <t>58363 (1 DIAS)+70,000 10 CARITAS+ 10,000 DOTACION+20,000 SUGERIDOS+155,272</t>
+  </si>
+  <si>
+    <t>COMISION PAGADA</t>
   </si>
 </sst>
 </file>
@@ -687,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E263F044-EB2C-4A38-BF1B-A61CE6B829F6}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
@@ -740,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>10</v>
@@ -749,10 +783,10 @@
         <v>11</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>12</v>
@@ -781,18 +815,17 @@
         <v>0</v>
       </c>
       <c r="H2" s="13">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="I2" s="20"/>
       <c r="J2" s="13">
         <f>+C2+D2+E2-F2+G2-H2</f>
-        <v>2360000.0000000005</v>
+        <v>3360000.0000000005</v>
       </c>
       <c r="K2" s="13">
         <v>0</v>
       </c>
       <c r="L2" s="13">
-        <f>K2-G2</f>
         <v>0</v>
       </c>
       <c r="M2" s="13">
@@ -807,7 +840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>94288721</v>
       </c>
@@ -830,33 +863,34 @@
         <v>700000</v>
       </c>
       <c r="H3" s="13">
-        <v>213889</v>
+        <v>0</v>
       </c>
       <c r="I3" s="21"/>
       <c r="J3" s="13">
-        <f t="shared" ref="J3:J19" si="0">+C3+D3+E3-F3+G3-H3</f>
-        <v>1346038.6</v>
+        <f t="shared" ref="J3:J18" si="0">+C3+D3+E3-F3+G3-H3</f>
+        <v>1559927.6</v>
       </c>
       <c r="K3" s="13">
-        <v>1702390</v>
+        <v>1569075</v>
       </c>
       <c r="L3" s="13">
-        <f t="shared" ref="L3:L21" si="1">K3-G3</f>
-        <v>1002390</v>
+        <v>869075</v>
       </c>
       <c r="M3" s="13">
-        <v>21000</v>
+        <v>42000</v>
       </c>
       <c r="N3" s="14">
-        <v>0</v>
-      </c>
-      <c r="O3" s="22"/>
+        <v>699217</v>
+      </c>
+      <c r="O3" s="22" t="s">
+        <v>45</v>
+      </c>
       <c r="P3" s="14">
         <f>L3-M3-N3</f>
-        <v>981390</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>127858</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1001200622</v>
       </c>
@@ -864,48 +898,51 @@
         <v>15</v>
       </c>
       <c r="C4" s="4">
-        <v>875452.5</v>
+        <v>700362</v>
       </c>
       <c r="D4" s="5">
-        <v>124547.49999999999</v>
+        <v>99638</v>
       </c>
       <c r="E4" s="13">
         <v>0</v>
       </c>
       <c r="F4" s="13">
-        <v>140072.4</v>
+        <v>126065.16</v>
       </c>
       <c r="G4" s="13">
         <v>600000</v>
       </c>
       <c r="H4" s="13">
-        <v>450000</v>
-      </c>
-      <c r="I4" s="22"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>35</v>
+      </c>
       <c r="J4" s="13">
         <f t="shared" si="0"/>
-        <v>1009927.6000000001</v>
+        <v>1273934.8399999999</v>
       </c>
       <c r="K4" s="13">
-        <v>1231400</v>
+        <v>1550000</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" si="1"/>
-        <v>631400</v>
+        <v>950000</v>
       </c>
       <c r="M4" s="13">
-        <v>35000</v>
+        <v>56000</v>
       </c>
       <c r="N4" s="14">
-        <v>0</v>
-      </c>
-      <c r="O4" s="25"/>
+        <v>601273</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="P4" s="14">
-        <f t="shared" ref="P4:P20" si="2">L4-M4-N4</f>
-        <v>596400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <f t="shared" ref="P4:P19" si="1">L4-M4-N4</f>
+        <v>292727</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1001045472</v>
       </c>
@@ -928,33 +965,34 @@
         <v>700000</v>
       </c>
       <c r="H5" s="13">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="I5" s="21"/>
       <c r="J5" s="13">
         <f t="shared" si="0"/>
-        <v>1259927.6000000001</v>
+        <v>1559927.6</v>
       </c>
       <c r="K5" s="13">
-        <v>1290748</v>
+        <v>1424889</v>
       </c>
       <c r="L5" s="13">
+        <v>724889</v>
+      </c>
+      <c r="M5" s="13">
+        <v>156363</v>
+      </c>
+      <c r="N5" s="14">
+        <v>101305</v>
+      </c>
+      <c r="O5" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" s="14">
         <f t="shared" si="1"/>
-        <v>590748</v>
-      </c>
-      <c r="M5" s="13">
-        <v>151726</v>
-      </c>
-      <c r="N5" s="14">
-        <v>0</v>
-      </c>
-      <c r="O5" s="22"/>
-      <c r="P5" s="14">
-        <f t="shared" si="2"/>
-        <v>439022</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>467221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>80875830</v>
       </c>
@@ -971,36 +1009,37 @@
         <v>0</v>
       </c>
       <c r="F6" s="13">
-        <v>135403.32</v>
+        <v>140072.4</v>
       </c>
       <c r="G6" s="13">
         <v>700000</v>
       </c>
       <c r="H6" s="13">
-        <v>392854</v>
+        <v>0</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>1171742.68</v>
+        <v>1559927.6</v>
       </c>
       <c r="K6" s="13">
-        <v>2232072</v>
+        <v>1673403</v>
       </c>
       <c r="L6" s="13">
+        <v>973403</v>
+      </c>
+      <c r="M6" s="13">
+        <v>42000</v>
+      </c>
+      <c r="N6" s="14">
+        <v>468722</v>
+      </c>
+      <c r="O6" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" s="14">
         <f t="shared" si="1"/>
-        <v>1532072</v>
-      </c>
-      <c r="M6" s="13">
-        <v>49000</v>
-      </c>
-      <c r="N6" s="14">
-        <v>0</v>
-      </c>
-      <c r="O6" s="22"/>
-      <c r="P6" s="14">
-        <f t="shared" si="2"/>
-        <v>1483072</v>
+        <v>462681</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1011,34 +1050,35 @@
         <v>18</v>
       </c>
       <c r="C7" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D7" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E7" s="13">
         <v>0</v>
       </c>
       <c r="F7" s="13">
-        <v>130734.24</v>
+        <v>135403.32</v>
       </c>
       <c r="G7" s="13">
         <v>100000</v>
       </c>
       <c r="H7" s="13">
-        <v>64822</v>
-      </c>
-      <c r="I7" s="21"/>
+        <v>7000</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>837777.09333333338</v>
+        <v>957596.67999999993</v>
       </c>
       <c r="K7" s="13">
         <v>0</v>
       </c>
       <c r="L7" s="13">
-        <f t="shared" si="1"/>
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="M7" s="13">
         <v>0</v>
@@ -1048,11 +1088,11 @@
       </c>
       <c r="O7" s="23"/>
       <c r="P7" s="14">
-        <f t="shared" si="2"/>
-        <v>-100000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1193092448</v>
       </c>
@@ -1075,30 +1115,31 @@
         <v>700000</v>
       </c>
       <c r="H8" s="13">
-        <v>488388</v>
+        <v>0</v>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>1071539.6000000001</v>
+        <v>1559927.6</v>
       </c>
       <c r="K8" s="13">
-        <v>0</v>
+        <v>1283900</v>
       </c>
       <c r="L8" s="13">
-        <f t="shared" si="1"/>
-        <v>-700000</v>
+        <v>583900</v>
       </c>
       <c r="M8" s="13">
-        <v>0</v>
+        <v>128363</v>
       </c>
       <c r="N8" s="14">
-        <v>0</v>
-      </c>
-      <c r="O8" s="25"/>
+        <v>185272</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>49</v>
+      </c>
       <c r="P8" s="14">
         <f>L8-M8-N8</f>
-        <v>-700000</v>
+        <v>270265</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1124,30 +1165,31 @@
         <v>300000</v>
       </c>
       <c r="H9" s="13">
-        <v>16000</v>
-      </c>
-      <c r="I9" s="22"/>
+        <v>63672</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>37</v>
+      </c>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
-        <v>1143927.6000000001</v>
+        <v>1096255.6000000001</v>
       </c>
       <c r="K9" s="13">
-        <v>326404</v>
+        <v>0</v>
       </c>
       <c r="L9" s="13">
-        <f t="shared" si="1"/>
-        <v>26404</v>
+        <v>0</v>
       </c>
       <c r="M9" s="13">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="N9" s="14">
         <v>0</v>
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="14">
-        <f t="shared" si="2"/>
-        <v>12404</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1158,7 +1200,7 @@
         <v>21</v>
       </c>
       <c r="C10" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D10" s="5">
         <v>116244.33333333333</v>
@@ -1167,18 +1209,20 @@
         <v>0</v>
       </c>
       <c r="F10" s="13">
-        <v>121396.08</v>
+        <v>135403.32</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
       </c>
       <c r="H10" s="13">
-        <v>58000</v>
-      </c>
-      <c r="I10" s="21"/>
+        <v>56000</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>38</v>
+      </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>812300.75333333341</v>
+        <v>741930.01333333342</v>
       </c>
       <c r="K10" s="13">
         <v>0</v>
@@ -1194,7 +1238,7 @@
       </c>
       <c r="O10" s="22"/>
       <c r="P10" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1232,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="13">
-        <v>0</v>
+        <v>113797</v>
       </c>
       <c r="M11" s="13">
         <v>0</v>
@@ -1240,10 +1284,12 @@
       <c r="N11" s="14">
         <v>0</v>
       </c>
-      <c r="O11" s="23"/>
+      <c r="O11" s="23" t="s">
+        <v>50</v>
+      </c>
       <c r="P11" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>113797</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -1280,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="13">
-        <v>0</v>
+        <v>572000</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
@@ -1290,8 +1336,8 @@
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>572000</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1302,27 +1348,29 @@
         <v>24</v>
       </c>
       <c r="C13" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D13" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E13" s="13">
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>135403.32</v>
+        <v>140072.4</v>
       </c>
       <c r="G13" s="13">
         <v>100000</v>
       </c>
       <c r="H13" s="13">
-        <v>7000</v>
-      </c>
-      <c r="I13" s="20"/>
+        <v>14000</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>39</v>
+      </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>890930.01333333342</v>
+        <v>945927.6</v>
       </c>
       <c r="K13" s="13">
         <v>0</v>
@@ -1338,7 +1386,7 @@
       </c>
       <c r="O13" s="23"/>
       <c r="P13" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1386,7 +1434,7 @@
       </c>
       <c r="O14" s="23"/>
       <c r="P14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1413,12 +1461,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="13">
-        <v>35000</v>
-      </c>
-      <c r="I15" s="22"/>
+        <v>280000</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="J15" s="13">
         <f t="shared" si="0"/>
-        <v>824927.6</v>
+        <v>579927.6</v>
       </c>
       <c r="K15" s="13">
         <v>0</v>
@@ -1434,7 +1484,7 @@
       </c>
       <c r="O15" s="23"/>
       <c r="P15" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1452,7 +1502,7 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E16" s="13">
-        <v>396543</v>
+        <v>400884</v>
       </c>
       <c r="F16" s="13">
         <v>140072.4</v>
@@ -1461,12 +1511,14 @@
         <v>0</v>
       </c>
       <c r="H16" s="13">
-        <v>28000</v>
-      </c>
-      <c r="I16" s="22"/>
+        <v>49000</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="J16" s="13">
         <f t="shared" si="0"/>
-        <v>1228470.6000000001</v>
+        <v>1211811.6000000001</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
@@ -1482,7 +1534,7 @@
       </c>
       <c r="O16" s="23"/>
       <c r="P16" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1494,27 +1546,29 @@
         <v>28</v>
       </c>
       <c r="C17" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D17" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E17" s="13">
-        <v>337121</v>
+        <v>364619</v>
       </c>
       <c r="F17" s="13">
-        <v>135403.32</v>
+        <v>140072.4</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="13">
-        <v>291147</v>
-      </c>
-      <c r="I17" s="22"/>
+        <v>7000</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>36</v>
+      </c>
       <c r="J17" s="13">
         <f t="shared" si="0"/>
-        <v>843904.01333333342</v>
+        <v>1217546.6000000001</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
@@ -1530,7 +1584,7 @@
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1542,27 +1596,29 @@
         <v>29</v>
       </c>
       <c r="C18" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D18" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E18" s="13">
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>135403.32</v>
+        <v>140072.4</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="13">
-        <v>112992</v>
-      </c>
-      <c r="I18" s="22"/>
+        <v>50000</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="J18" s="13">
         <f t="shared" si="0"/>
-        <v>684938.01333333342</v>
+        <v>809927.6</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
@@ -1578,45 +1634,46 @@
       </c>
       <c r="O18" s="23"/>
       <c r="P18" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>1003950486</v>
+        <v>1053330769</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D19" s="5">
         <v>116244.33333333333</v>
       </c>
       <c r="E19" s="13">
-        <v>308031</v>
+        <v>345302</v>
       </c>
       <c r="F19" s="13">
-        <v>140072.4</v>
+        <v>135403.32</v>
       </c>
       <c r="G19" s="13">
         <v>0</v>
       </c>
       <c r="H19" s="13">
-        <v>0</v>
-      </c>
-      <c r="I19" s="22"/>
+        <v>131359</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>43</v>
+      </c>
       <c r="J19" s="13">
-        <f t="shared" si="0"/>
-        <v>1159655.4333333336</v>
+        <f>+C19+D19+E19-F19+G19-H19</f>
+        <v>1011873.0133333334</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
       </c>
       <c r="L19" s="13">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M19" s="13">
@@ -1627,25 +1684,25 @@
       </c>
       <c r="O19" s="23"/>
       <c r="P19" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>1053330769</v>
+        <v>1013673759</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C20" s="4">
         <v>875452.5</v>
       </c>
       <c r="D20" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E20" s="13">
-        <v>361288</v>
+        <v>0</v>
       </c>
       <c r="F20" s="13">
         <v>140072.4</v>
@@ -1654,18 +1711,19 @@
         <v>0</v>
       </c>
       <c r="H20" s="13">
-        <v>151729</v>
-      </c>
-      <c r="I20" s="22"/>
+        <v>88000</v>
+      </c>
+      <c r="I20" s="22" t="s">
+        <v>44</v>
+      </c>
       <c r="J20" s="13">
         <f>+C20+D20+E20-F20+G20-H20</f>
-        <v>1061183.4333333336</v>
+        <v>771927.6</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>
       </c>
       <c r="L20" s="13">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M20" s="13">
@@ -1676,75 +1734,26 @@
       </c>
       <c r="O20" s="23"/>
       <c r="P20" s="14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>1013673759</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="4">
-        <v>466908</v>
-      </c>
-      <c r="D21" s="5">
-        <v>66425.333333333328</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
-        <v>37352.639999999999</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <v>150000</v>
-      </c>
-      <c r="I21" s="22"/>
-      <c r="J21" s="13">
-        <f>+C21+D21+E21-F21+G21-H21</f>
-        <v>345980.69333333336</v>
-      </c>
-      <c r="K21" s="13">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="13">
-        <v>0</v>
-      </c>
-      <c r="N21" s="14">
-        <v>0</v>
-      </c>
-      <c r="O21" s="23"/>
-      <c r="P21" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9884A3-91E5-48CA-925A-244D94946A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D953C15-A58A-48D7-BDEF-EE53B0665D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>CEDULA</t>
   </si>
@@ -132,52 +132,55 @@
     <t>BRYAN ALEJANDRO SANCHEZ GARCIA</t>
   </si>
   <si>
-    <t>3 DIAS VACACIONES</t>
-  </si>
-  <si>
-    <t>7,000 1 CARITA</t>
-  </si>
-  <si>
-    <t>21,000 3 CARITAS+20,000 SUGERIDOS+22,672  EXCENDE BONO</t>
-  </si>
-  <si>
-    <t>1 DIA LCNR+7,000 1 CARITA+22,000 SUGERIDOS+27,000 VALES</t>
-  </si>
-  <si>
-    <t>14,000 2 CARITAS</t>
-  </si>
-  <si>
-    <t>28,000 4 CARITAS</t>
-  </si>
-  <si>
-    <t>49,000 7 CARITAS</t>
-  </si>
-  <si>
-    <t>28,000 4 CARITAS+22,000 SUGERIDOS</t>
-  </si>
-  <si>
-    <t>1 DIA LCNR+ 58,363 (1 DIAS)+63,000 9 CARITAS+9996 Dominical</t>
-  </si>
-  <si>
-    <t>28,000 4 CARITAS+10,000 VALES+50,000 VALES</t>
-  </si>
-  <si>
-    <t>42,000 6 CARITAS+6,391 UTILIDADES+10,000 SUGERIDO+682,826 VALES</t>
-  </si>
-  <si>
-    <t>10,000 DOTACION+56,000 8 CARITAS+119,810 UTILIDADES+22,000 SUGERIDOS+449,463 VALES</t>
-  </si>
-  <si>
-    <t>58,363 (1 DIAS)+  98,000 14 CARITAS+101,305 VALES</t>
-  </si>
-  <si>
-    <t>42,000 6 CARITAS+20,722 UTILIDADES+48,000 SUGERIDO+400,000 VALES</t>
-  </si>
-  <si>
-    <t>58363 (1 DIAS)+70,000 10 CARITAS+ 10,000 DOTACION+20,000 SUGERIDOS+155,272</t>
-  </si>
-  <si>
-    <t>COMISION PAGADA</t>
+    <t>1,324,000 VALES</t>
+  </si>
+  <si>
+    <t>35,300 COOSERPARK +20,000 DONACION+217,000 PRESTAMO+76,850 VALES</t>
+  </si>
+  <si>
+    <t>44,700 COOSERPARK+20,000 DONACION+291,229 VALES</t>
+  </si>
+  <si>
+    <t>20.000 DONACION+1 DIA LCNR+9922 DOMINICAL</t>
+  </si>
+  <si>
+    <t>3 DIAS VACAS+139,362 VALES</t>
+  </si>
+  <si>
+    <t>44,700 COOSERPARK+20,000 DONACION</t>
+  </si>
+  <si>
+    <t>35,300 COOSERPARK +20,000 DONACION+34,760 PLAN CELULAR</t>
+  </si>
+  <si>
+    <t>20.000 DONACION</t>
+  </si>
+  <si>
+    <t>27,000 VALES+150,000 CARTERA AURA</t>
+  </si>
+  <si>
+    <t>20.000 DONACION+600,000 VALE</t>
+  </si>
+  <si>
+    <t>100,000 DONACION</t>
+  </si>
+  <si>
+    <t>20.000 DONACION+194,654 VALE</t>
+  </si>
+  <si>
+    <t>20.000 DONACION+213,600 PRESTAMO+23,000 VALE</t>
+  </si>
+  <si>
+    <t>70,000 DONACION+183,670 PRESTAMO</t>
+  </si>
+  <si>
+    <t>60,000 VALES</t>
+  </si>
+  <si>
+    <t>1 DIA AUSENCIA+DOMINICAL+2 DIAS INCP+200,000 VALES</t>
+  </si>
+  <si>
+    <t>20,000 DONACION+1 DIA LCNR+9922 DOMINICAL+100,000 VALES</t>
   </si>
 </sst>
 </file>
@@ -809,18 +812,20 @@
         <v>0</v>
       </c>
       <c r="F2" s="13">
-        <v>640000.00000000012</v>
+        <v>0</v>
       </c>
       <c r="G2" s="13">
         <v>0</v>
       </c>
       <c r="H2" s="13">
-        <v>0</v>
-      </c>
-      <c r="I2" s="20"/>
+        <v>1324000</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>35</v>
+      </c>
       <c r="J2" s="13">
         <f>+C2+D2+E2-F2+G2-H2</f>
-        <v>3360000.0000000005</v>
+        <v>2676000.0000000005</v>
       </c>
       <c r="K2" s="13">
         <v>0</v>
@@ -857,40 +862,41 @@
         <v>0</v>
       </c>
       <c r="F3" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="13">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H3" s="13">
-        <v>0</v>
-      </c>
-      <c r="I3" s="21"/>
+        <f>313850+35300</f>
+        <v>349150</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="J3" s="13">
         <f t="shared" ref="J3:J18" si="0">+C3+D3+E3-F3+G3-H3</f>
-        <v>1559927.6</v>
+        <v>650850</v>
       </c>
       <c r="K3" s="13">
-        <v>1569075</v>
+        <v>0</v>
       </c>
       <c r="L3" s="13">
-        <v>869075</v>
+        <v>0</v>
       </c>
       <c r="M3" s="13">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="N3" s="14">
-        <v>699217</v>
-      </c>
-      <c r="O3" s="22" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O3" s="22"/>
       <c r="P3" s="14">
         <f>L3-M3-N3</f>
-        <v>127858</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1001200622</v>
       </c>
@@ -898,51 +904,50 @@
         <v>15</v>
       </c>
       <c r="C4" s="4">
-        <v>700362</v>
+        <v>875452.5</v>
       </c>
       <c r="D4" s="5">
-        <v>99638</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E4" s="13">
         <v>0</v>
       </c>
       <c r="F4" s="13">
-        <v>126065.16</v>
+        <v>0</v>
       </c>
       <c r="G4" s="13">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="H4" s="13">
-        <v>0</v>
+        <f>311229+44700</f>
+        <v>355929</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J4" s="13">
         <f t="shared" si="0"/>
-        <v>1273934.8399999999</v>
+        <v>644071</v>
       </c>
       <c r="K4" s="13">
-        <v>1550000</v>
+        <v>0</v>
       </c>
       <c r="L4" s="13">
-        <v>950000</v>
+        <v>0</v>
       </c>
       <c r="M4" s="13">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="N4" s="14">
-        <v>601273</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>46</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O4" s="25"/>
       <c r="P4" s="14">
         <f t="shared" ref="P4:P19" si="1">L4-M4-N4</f>
-        <v>292727</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1001045472</v>
       </c>
@@ -950,49 +955,49 @@
         <v>16</v>
       </c>
       <c r="C5" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D5" s="5">
-        <v>124547.49999999999</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E5" s="13">
         <v>0</v>
       </c>
       <c r="F5" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="13">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="13">
-        <v>0</v>
-      </c>
-      <c r="I5" s="21"/>
+        <v>29922</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>38</v>
+      </c>
       <c r="J5" s="13">
         <f t="shared" si="0"/>
-        <v>1559927.6</v>
+        <v>903411.33333333337</v>
       </c>
       <c r="K5" s="13">
-        <v>1424889</v>
+        <v>0</v>
       </c>
       <c r="L5" s="13">
-        <v>724889</v>
+        <v>0</v>
       </c>
       <c r="M5" s="13">
-        <v>156363</v>
+        <v>0</v>
       </c>
       <c r="N5" s="14">
-        <v>101305</v>
-      </c>
-      <c r="O5" s="22" t="s">
-        <v>47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O5" s="22"/>
       <c r="P5" s="14">
         <f t="shared" si="1"/>
-        <v>467221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>80875830</v>
       </c>
@@ -1000,46 +1005,46 @@
         <v>17</v>
       </c>
       <c r="C6" s="4">
-        <v>875452.5</v>
+        <v>700362</v>
       </c>
       <c r="D6" s="5">
-        <v>124547.49999999999</v>
+        <v>91334.833333333328</v>
       </c>
       <c r="E6" s="13">
         <v>0</v>
       </c>
       <c r="F6" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="13">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H6" s="13">
-        <v>0</v>
-      </c>
-      <c r="I6" s="23"/>
+        <v>159362</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>39</v>
+      </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>1559927.6</v>
+        <v>632334.83333333337</v>
       </c>
       <c r="K6" s="13">
-        <v>1673403</v>
+        <v>0</v>
       </c>
       <c r="L6" s="13">
-        <v>973403</v>
+        <v>0</v>
       </c>
       <c r="M6" s="13">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="N6" s="14">
-        <v>468722</v>
-      </c>
-      <c r="O6" s="22" t="s">
-        <v>48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6" s="22"/>
       <c r="P6" s="14">
         <f t="shared" si="1"/>
-        <v>462681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1059,20 +1064,21 @@
         <v>0</v>
       </c>
       <c r="F7" s="13">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G7" s="13">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="13">
-        <v>7000</v>
+        <f>20000+44700</f>
+        <v>64700</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>957596.67999999993</v>
+        <v>935300</v>
       </c>
       <c r="K7" s="13">
         <v>0</v>
@@ -1092,7 +1098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1193092448</v>
       </c>
@@ -1109,37 +1115,38 @@
         <v>0</v>
       </c>
       <c r="F8" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="13">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="24"/>
+        <f>316755+35300</f>
+        <v>352055</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>41</v>
+      </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>1559927.6</v>
+        <v>647945</v>
       </c>
       <c r="K8" s="13">
-        <v>1283900</v>
+        <v>0</v>
       </c>
       <c r="L8" s="13">
-        <v>583900</v>
+        <v>0</v>
       </c>
       <c r="M8" s="13">
-        <v>128363</v>
+        <v>0</v>
       </c>
       <c r="N8" s="14">
-        <v>185272</v>
-      </c>
-      <c r="O8" s="25" t="s">
-        <v>49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O8" s="25"/>
       <c r="P8" s="14">
         <f>L8-M8-N8</f>
-        <v>270265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1159,20 +1166,20 @@
         <v>0</v>
       </c>
       <c r="F9" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="13">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="13">
-        <v>63672</v>
+        <v>20000</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
-        <v>1096255.6000000001</v>
+        <v>980000</v>
       </c>
       <c r="K9" s="13">
         <v>0</v>
@@ -1200,29 +1207,29 @@
         <v>21</v>
       </c>
       <c r="C10" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D10" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E10" s="13">
         <v>0</v>
       </c>
       <c r="F10" s="13">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
       </c>
       <c r="H10" s="13">
-        <v>56000</v>
+        <v>177000</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>741930.01333333342</v>
+        <v>823000</v>
       </c>
       <c r="K10" s="13">
         <v>0</v>
@@ -1259,24 +1266,22 @@
         <v>0</v>
       </c>
       <c r="F11" s="13">
-        <v>172000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="13">
-        <v>850000</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H11" s="13"/>
       <c r="I11" s="20"/>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>1877547.5</v>
+        <v>1199547.5</v>
       </c>
       <c r="K11" s="13">
         <v>0</v>
       </c>
       <c r="L11" s="13">
-        <v>113797</v>
+        <v>0</v>
       </c>
       <c r="M11" s="13">
         <v>0</v>
@@ -1284,12 +1289,10 @@
       <c r="N11" s="14">
         <v>0</v>
       </c>
-      <c r="O11" s="23" t="s">
-        <v>50</v>
-      </c>
+      <c r="O11" s="23"/>
       <c r="P11" s="14">
         <f t="shared" si="1"/>
-        <v>113797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -1300,7 +1303,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>7150000</v>
+        <v>0</v>
       </c>
       <c r="D12" s="5">
         <v>0</v>
@@ -1309,24 +1312,22 @@
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="13">
-        <v>2000000</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H12" s="13"/>
       <c r="I12" s="26"/>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>8578000</v>
+        <v>0</v>
       </c>
       <c r="K12" s="13">
         <v>0</v>
       </c>
       <c r="L12" s="13">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
@@ -1337,7 +1338,7 @@
       <c r="O12" s="23"/>
       <c r="P12" s="14">
         <f t="shared" si="1"/>
-        <v>572000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1357,20 +1358,20 @@
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G13" s="13">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H13" s="13">
-        <v>14000</v>
+        <v>620000</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>945927.6</v>
+        <v>380000</v>
       </c>
       <c r="K13" s="13">
         <v>0</v>
@@ -1407,18 +1408,20 @@
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="G14" s="13">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="23"/>
+        <v>100000</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>45</v>
+      </c>
       <c r="J14" s="13">
         <f t="shared" si="0"/>
-        <v>1648547.5</v>
+        <v>1124547.5</v>
       </c>
       <c r="K14" s="13">
         <v>0</v>
@@ -1455,20 +1458,20 @@
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
       <c r="H15" s="13">
-        <v>280000</v>
+        <v>214659</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="0"/>
-        <v>579927.6</v>
+        <v>785341</v>
       </c>
       <c r="K15" s="13">
         <v>0</v>
@@ -1502,23 +1505,23 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E16" s="13">
-        <v>400884</v>
+        <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
       <c r="H16" s="13">
-        <v>49000</v>
+        <v>256600</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J16" s="13">
         <f t="shared" si="0"/>
-        <v>1211811.6000000001</v>
+        <v>743400</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
@@ -1552,23 +1555,23 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E17" s="13">
-        <v>364619</v>
+        <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="13">
-        <v>7000</v>
+        <v>253670</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J17" s="13">
         <f t="shared" si="0"/>
-        <v>1217546.6000000001</v>
+        <v>746330</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
@@ -1605,20 +1608,20 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="13">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="0"/>
-        <v>809927.6</v>
+        <v>940000</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
@@ -1646,29 +1649,29 @@
         <v>30</v>
       </c>
       <c r="C19" s="4">
-        <v>817089</v>
+        <v>758725.5</v>
       </c>
       <c r="D19" s="5">
-        <v>116244.33333333333</v>
+        <v>91334.833333333328</v>
       </c>
       <c r="E19" s="13">
-        <v>345302</v>
+        <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G19" s="13">
         <v>0</v>
       </c>
       <c r="H19" s="13">
-        <v>131359</v>
+        <v>200000</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J19" s="13">
         <f>+C19+D19+E19-F19+G19-H19</f>
-        <v>1011873.0133333334</v>
+        <v>650060.33333333337</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
@@ -1696,29 +1699,29 @@
         <v>34</v>
       </c>
       <c r="C20" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D20" s="5">
-        <v>124547.49999999999</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="13">
         <v>0</v>
       </c>
       <c r="H20" s="13">
-        <v>88000</v>
+        <v>129922</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J20" s="13">
         <f>+C20+D20+E20-F20+G20-H20</f>
-        <v>771927.6</v>
+        <v>803411.33333333337</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D953C15-A58A-48D7-BDEF-EE53B0665D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BED8768-C3CC-4B89-9F92-7130CAB743E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>CEDULA</t>
   </si>
@@ -132,55 +132,70 @@
     <t>BRYAN ALEJANDRO SANCHEZ GARCIA</t>
   </si>
   <si>
-    <t>1,324,000 VALES</t>
-  </si>
-  <si>
-    <t>35,300 COOSERPARK +20,000 DONACION+217,000 PRESTAMO+76,850 VALES</t>
-  </si>
-  <si>
-    <t>44,700 COOSERPARK+20,000 DONACION+291,229 VALES</t>
-  </si>
-  <si>
-    <t>20.000 DONACION+1 DIA LCNR+9922 DOMINICAL</t>
-  </si>
-  <si>
-    <t>3 DIAS VACAS+139,362 VALES</t>
-  </si>
-  <si>
-    <t>44,700 COOSERPARK+20,000 DONACION</t>
-  </si>
-  <si>
-    <t>35,300 COOSERPARK +20,000 DONACION+34,760 PLAN CELULAR</t>
-  </si>
-  <si>
-    <t>20.000 DONACION</t>
-  </si>
-  <si>
-    <t>27,000 VALES+150,000 CARTERA AURA</t>
-  </si>
-  <si>
-    <t>20.000 DONACION+600,000 VALE</t>
-  </si>
-  <si>
-    <t>100,000 DONACION</t>
-  </si>
-  <si>
-    <t>20.000 DONACION+194,654 VALE</t>
-  </si>
-  <si>
-    <t>20.000 DONACION+213,600 PRESTAMO+23,000 VALE</t>
-  </si>
-  <si>
-    <t>70,000 DONACION+183,670 PRESTAMO</t>
-  </si>
-  <si>
-    <t>60,000 VALES</t>
-  </si>
-  <si>
-    <t>1 DIA AUSENCIA+DOMINICAL+2 DIAS INCP+200,000 VALES</t>
-  </si>
-  <si>
-    <t>20,000 DONACION+1 DIA LCNR+9922 DOMINICAL+100,000 VALES</t>
+    <t>MICHEL STEVEN HERNANDEZ ROJAS</t>
+  </si>
+  <si>
+    <t>360,000 VALES</t>
+  </si>
+  <si>
+    <t>250,000 PRESTAMO+7,000 CARITAS</t>
+  </si>
+  <si>
+    <t>40,798 UTILIDADES+63,000 CARITAS+700,000 BONO+30,000 DOTACION+20,000 SUGERIDOS</t>
+  </si>
+  <si>
+    <t>1 DIA VC+56,000 CARITAS+300,000 BONO+20,000 SUGERIDOS</t>
+  </si>
+  <si>
+    <t>19,000 SUGERIDOS+102,320 INVENTARIO</t>
+  </si>
+  <si>
+    <t>196,694 COMISION</t>
+  </si>
+  <si>
+    <t>14,000 CARITAS</t>
+  </si>
+  <si>
+    <t>VAC</t>
+  </si>
+  <si>
+    <t>113,000 VALES+1 DIA AUSEN+1 DOMINICAL+49,000 CARITAS+20,822 VALES</t>
+  </si>
+  <si>
+    <t>210,200 PRESTAMO+42,000 CARITAS</t>
+  </si>
+  <si>
+    <t>180,833 PRESTAMO+7,000 CARITAS+3000 SUGERIDOS</t>
+  </si>
+  <si>
+    <t>RENUNCIA 20 AGOS+60,000 VALES+50,000 CAMISA DOTACION ROTA+2,500 UTILIDADES+14,000 CARITAS+14,000 SUGERIDOS</t>
+  </si>
+  <si>
+    <t>100,363 CARITAS+50,000 DOTACION</t>
+  </si>
+  <si>
+    <t>140,000 VALES+21,000 CARITAS+10,000 DOTACION+48,586 VALES</t>
+  </si>
+  <si>
+    <t>INGRESO EL 27 AGOS</t>
+  </si>
+  <si>
+    <t>213,600 PRESTAMO+28,000 CARITAS+10,000 DOTACION+4,000 SUGERIDOS+237,974 VALES</t>
+  </si>
+  <si>
+    <t>89,297 UTILIDADES+42,000 CARITAS+10,000 DOTACION+12,000 SUGERIDOS+228,860 VALES</t>
+  </si>
+  <si>
+    <t>56,000 CARITAS+10,000 DOTACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,808 UTILIDADES+56,000 DANIEL+10,000 DOTACION+32,000 SUGERIDOS+547.274 VALES </t>
+  </si>
+  <si>
+    <t>DEVOL VACACIONES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109,376 ABONA A VALES </t>
   </si>
 </sst>
 </file>
@@ -193,7 +208,7 @@
     <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +261,12 @@
       <color rgb="FFFF0000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -306,7 +327,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -385,6 +406,15 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -724,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E263F044-EB2C-4A38-BF1B-A61CE6B829F6}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
@@ -740,7 +770,7 @@
     <col min="11" max="12" width="19.85546875" style="18" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.140625" style="18" customWidth="1"/>
     <col min="14" max="14" width="15.28515625" style="10" customWidth="1"/>
-    <col min="15" max="15" width="41.42578125" style="10" customWidth="1"/>
+    <col min="15" max="15" width="44.5703125" style="10" customWidth="1"/>
     <col min="16" max="16" width="15.85546875" style="10" customWidth="1"/>
     <col min="17" max="16384" width="11.42578125" style="10"/>
   </cols>
@@ -812,20 +842,19 @@
         <v>0</v>
       </c>
       <c r="F2" s="13">
-        <v>0</v>
+        <v>640000.00000000012</v>
       </c>
       <c r="G2" s="13">
         <v>0</v>
       </c>
       <c r="H2" s="13">
-        <v>1324000</v>
+        <v>360000</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2" s="13">
-        <f>+C2+D2+E2-F2+G2-H2</f>
-        <v>2676000.0000000005</v>
+        <v>3000000.0000000005</v>
       </c>
       <c r="K2" s="13">
         <v>0</v>
@@ -862,41 +891,37 @@
         <v>0</v>
       </c>
       <c r="F3" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G3" s="13">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13">
-        <f>313850+35300</f>
-        <v>349150</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>36</v>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="H3" s="13"/>
+      <c r="I3" s="21"/>
       <c r="J3" s="13">
-        <f t="shared" ref="J3:J18" si="0">+C3+D3+E3-F3+G3-H3</f>
-        <v>650850</v>
+        <v>1559927.6</v>
       </c>
       <c r="K3" s="13">
-        <v>0</v>
+        <v>1550000</v>
       </c>
       <c r="L3" s="13">
-        <v>0</v>
+        <v>850000</v>
       </c>
       <c r="M3" s="13">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="N3" s="14">
-        <v>0</v>
-      </c>
-      <c r="O3" s="22"/>
+        <v>465574</v>
+      </c>
+      <c r="O3" s="22" t="s">
+        <v>51</v>
+      </c>
       <c r="P3" s="14">
         <f>L3-M3-N3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>356426</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1001200622</v>
       </c>
@@ -913,38 +938,34 @@
         <v>0</v>
       </c>
       <c r="F4" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G4" s="13">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13">
-        <f>311229+44700</f>
-        <v>355929</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>37</v>
-      </c>
+        <v>600000</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="22"/>
       <c r="J4" s="13">
-        <f t="shared" si="0"/>
-        <v>644071</v>
+        <v>1459927.6</v>
       </c>
       <c r="K4" s="13">
-        <v>0</v>
+        <v>1250000</v>
       </c>
       <c r="L4" s="13">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="M4" s="13">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="N4" s="14">
-        <v>0</v>
-      </c>
-      <c r="O4" s="25"/>
+        <v>340157</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>52</v>
+      </c>
       <c r="P4" s="14">
-        <f t="shared" ref="P4:P19" si="1">L4-M4-N4</f>
-        <v>0</v>
+        <f t="shared" ref="P4:P19" si="0">L4-M4-N4</f>
+        <v>267843</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -955,49 +976,46 @@
         <v>16</v>
       </c>
       <c r="C5" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D5" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E5" s="13">
         <v>0</v>
       </c>
       <c r="F5" s="13">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G5" s="13">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
-        <v>29922</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>38</v>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="21"/>
       <c r="J5" s="13">
+        <v>1564596.68</v>
+      </c>
+      <c r="K5" s="13">
+        <v>1269670</v>
+      </c>
+      <c r="L5" s="13">
+        <v>569670</v>
+      </c>
+      <c r="M5" s="13">
+        <v>56000</v>
+      </c>
+      <c r="N5" s="14">
+        <v>10000</v>
+      </c>
+      <c r="O5" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="P5" s="14">
         <f t="shared" si="0"/>
-        <v>903411.33333333337</v>
-      </c>
-      <c r="K5" s="13">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
-        <v>0</v>
-      </c>
-      <c r="M5" s="13">
-        <v>0</v>
-      </c>
-      <c r="N5" s="14">
-        <v>0</v>
-      </c>
-      <c r="O5" s="22"/>
-      <c r="P5" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>503670</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>80875830</v>
       </c>
@@ -1005,46 +1023,43 @@
         <v>17</v>
       </c>
       <c r="C6" s="4">
-        <v>700362</v>
+        <v>875452.5</v>
       </c>
       <c r="D6" s="5">
-        <v>91334.833333333328</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E6" s="13">
         <v>0</v>
       </c>
       <c r="F6" s="13">
-        <v>0</v>
+        <v>126065.16</v>
       </c>
       <c r="G6" s="13">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
-        <v>159362</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>39</v>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="23"/>
       <c r="J6" s="13">
+        <v>1573934.84</v>
+      </c>
+      <c r="K6" s="13">
+        <v>1739070</v>
+      </c>
+      <c r="L6" s="13">
+        <v>1039070</v>
+      </c>
+      <c r="M6" s="13">
+        <v>56000</v>
+      </c>
+      <c r="N6" s="14">
+        <v>598082</v>
+      </c>
+      <c r="O6" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="14">
         <f t="shared" si="0"/>
-        <v>632334.83333333337</v>
-      </c>
-      <c r="K6" s="13">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
-        <v>0</v>
-      </c>
-      <c r="M6" s="13">
-        <v>0</v>
-      </c>
-      <c r="N6" s="14">
-        <v>0</v>
-      </c>
-      <c r="O6" s="22"/>
-      <c r="P6" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>384988</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1064,21 +1079,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G7" s="13">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H7" s="13">
-        <f>20000+44700</f>
-        <v>64700</v>
+        <v>257000</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J7" s="13">
-        <f t="shared" si="0"/>
-        <v>935300</v>
+        <v>702927.6</v>
       </c>
       <c r="K7" s="13">
         <v>0</v>
@@ -1094,11 +1107,11 @@
       </c>
       <c r="O7" s="23"/>
       <c r="P7" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1193092448</v>
       </c>
@@ -1115,21 +1128,19 @@
         <v>0</v>
       </c>
       <c r="F8" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G8" s="13">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="H8" s="13">
-        <f>316755+35300</f>
-        <v>352055</v>
+        <v>853798</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J8" s="13">
-        <f t="shared" si="0"/>
-        <v>647945</v>
+        <v>706129.6</v>
       </c>
       <c r="K8" s="13">
         <v>0</v>
@@ -1157,29 +1168,28 @@
         <v>20</v>
       </c>
       <c r="C9" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D9" s="5">
-        <v>124547.49999999999</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E9" s="13">
         <v>0</v>
       </c>
       <c r="F9" s="13">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G9" s="13">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="H9" s="13">
-        <v>20000</v>
+        <v>376000</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J9" s="13">
-        <f t="shared" si="0"/>
-        <v>980000</v>
+        <v>721930.01333333342</v>
       </c>
       <c r="K9" s="13">
         <v>0</v>
@@ -1195,7 +1205,7 @@
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1216,20 +1226,19 @@
         <v>0</v>
       </c>
       <c r="F10" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
       </c>
       <c r="H10" s="13">
-        <v>177000</v>
+        <v>121340</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J10" s="13">
-        <f t="shared" si="0"/>
-        <v>823000</v>
+        <v>738587.6</v>
       </c>
       <c r="K10" s="13">
         <v>0</v>
@@ -1245,7 +1254,7 @@
       </c>
       <c r="O10" s="22"/>
       <c r="P10" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1266,16 +1275,17 @@
         <v>0</v>
       </c>
       <c r="F11" s="13">
-        <v>0</v>
+        <v>172000</v>
       </c>
       <c r="G11" s="13">
-        <v>0</v>
+        <v>850000</v>
       </c>
       <c r="H11" s="13"/>
-      <c r="I11" s="20"/>
+      <c r="I11" s="20" t="s">
+        <v>41</v>
+      </c>
       <c r="J11" s="13">
-        <f t="shared" si="0"/>
-        <v>1199547.5</v>
+        <v>1877547.5</v>
       </c>
       <c r="K11" s="13">
         <v>0</v>
@@ -1291,7 +1301,7 @@
       </c>
       <c r="O11" s="23"/>
       <c r="P11" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1303,7 +1313,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
+        <v>7150000</v>
       </c>
       <c r="D12" s="5">
         <v>0</v>
@@ -1312,22 +1322,21 @@
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>0</v>
+        <v>572000</v>
       </c>
       <c r="G12" s="13">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="26"/>
       <c r="J12" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8578000</v>
       </c>
       <c r="K12" s="13">
         <v>0</v>
       </c>
-      <c r="L12" s="13">
-        <v>0</v>
+      <c r="L12" s="28">
+        <v>572000</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
@@ -1337,8 +1346,8 @@
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>572000</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1358,25 +1367,24 @@
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G13" s="13">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H13" s="13">
-        <v>620000</v>
+        <v>14000</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J13" s="13">
-        <f t="shared" si="0"/>
-        <v>380000</v>
+        <v>945927.6</v>
       </c>
       <c r="K13" s="13">
         <v>0</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="29">
         <v>0</v>
       </c>
       <c r="M13" s="13">
@@ -1387,7 +1395,7 @@
       </c>
       <c r="O13" s="23"/>
       <c r="P13" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1399,49 +1407,49 @@
         <v>25</v>
       </c>
       <c r="C14" s="4">
-        <v>1100000</v>
+        <v>366666.66666666663</v>
       </c>
       <c r="D14" s="5">
-        <v>124547.49999999999</v>
+        <v>41515.833333333328</v>
       </c>
       <c r="E14" s="13">
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>0</v>
+        <v>117333.33333333333</v>
       </c>
       <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>100000</v>
-      </c>
+        <v>600000</v>
+      </c>
+      <c r="H14" s="13"/>
       <c r="I14" s="23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J14" s="13">
+        <v>890849.16666666663</v>
+      </c>
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="28">
+        <f>733333+207579</f>
+        <v>940912</v>
+      </c>
+      <c r="M14" s="13">
+        <v>0</v>
+      </c>
+      <c r="N14" s="14">
+        <v>0</v>
+      </c>
+      <c r="O14" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="P14" s="14">
         <f t="shared" si="0"/>
-        <v>1124547.5</v>
-      </c>
-      <c r="K14" s="13">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13">
-        <v>0</v>
-      </c>
-      <c r="N14" s="14">
-        <v>0</v>
-      </c>
-      <c r="O14" s="23"/>
-      <c r="P14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>940912</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>1026306646</v>
       </c>
@@ -1449,34 +1457,33 @@
         <v>26</v>
       </c>
       <c r="C15" s="4">
-        <v>875452.5</v>
+        <v>758725.5</v>
       </c>
       <c r="D15" s="5">
-        <v>124547.49999999999</v>
+        <v>107941.16666666666</v>
       </c>
       <c r="E15" s="13">
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>0</v>
+        <v>130734.24</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
       <c r="H15" s="13">
-        <v>214659</v>
+        <v>182822</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="0"/>
-        <v>785341</v>
+        <v>553110.42666666664</v>
       </c>
       <c r="K15" s="13">
         <v>0</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="29">
         <v>0</v>
       </c>
       <c r="M15" s="13">
@@ -1487,7 +1494,7 @@
       </c>
       <c r="O15" s="23"/>
       <c r="P15" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1505,28 +1512,27 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E16" s="13">
-        <v>0</v>
+        <v>337043</v>
       </c>
       <c r="F16" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
       <c r="H16" s="13">
-        <v>256600</v>
+        <v>252200</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" si="0"/>
-        <v>743400</v>
+        <v>944770.6</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="29">
         <v>0</v>
       </c>
       <c r="M16" s="13">
@@ -1537,7 +1543,7 @@
       </c>
       <c r="O16" s="23"/>
       <c r="P16" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1555,43 +1561,44 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E17" s="13">
-        <v>0</v>
+        <v>160699</v>
       </c>
       <c r="F17" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="13">
-        <v>253670</v>
+        <v>190833</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J17" s="13">
+        <v>829793.6</v>
+      </c>
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="28">
+        <v>109376</v>
+      </c>
+      <c r="M17" s="13">
+        <v>109376</v>
+      </c>
+      <c r="N17" s="14">
+        <v>0</v>
+      </c>
+      <c r="O17" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="P17" s="14">
         <f t="shared" si="0"/>
-        <v>746330</v>
-      </c>
-      <c r="K17" s="13">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0</v>
-      </c>
-      <c r="M17" s="13">
-        <v>0</v>
-      </c>
-      <c r="N17" s="14">
-        <v>0</v>
-      </c>
-      <c r="O17" s="23"/>
-      <c r="P17" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>1123436140</v>
       </c>
@@ -1599,29 +1606,28 @@
         <v>29</v>
       </c>
       <c r="C18" s="4">
-        <v>875452.5</v>
+        <v>350181</v>
       </c>
       <c r="D18" s="5">
-        <v>124547.49999999999</v>
+        <v>49819</v>
       </c>
       <c r="E18" s="13">
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>0</v>
+        <v>98050.680000000008</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="13">
-        <v>60000</v>
+        <v>140500</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="0"/>
-        <v>940000</v>
+        <v>161449.32</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
@@ -1637,7 +1643,7 @@
       </c>
       <c r="O18" s="23"/>
       <c r="P18" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1649,29 +1655,28 @@
         <v>30</v>
       </c>
       <c r="C19" s="4">
-        <v>758725.5</v>
+        <v>875452.5</v>
       </c>
       <c r="D19" s="5">
-        <v>91334.833333333328</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E19" s="13">
-        <v>0</v>
+        <v>270810</v>
       </c>
       <c r="F19" s="13">
-        <v>0</v>
+        <v>130734.24</v>
       </c>
       <c r="G19" s="13">
         <v>0</v>
       </c>
       <c r="H19" s="13">
-        <v>200000</v>
+        <v>150363</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J19" s="13">
-        <f>+C19+D19+E19-F19+G19-H19</f>
-        <v>650060.33333333337</v>
+        <v>989712.76</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
@@ -1687,7 +1692,7 @@
       </c>
       <c r="O19" s="23"/>
       <c r="P19" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1699,29 +1704,28 @@
         <v>34</v>
       </c>
       <c r="C20" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D20" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G20" s="13">
         <v>0</v>
       </c>
       <c r="H20" s="13">
-        <v>129922</v>
+        <v>219586</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J20" s="13">
-        <f>+C20+D20+E20-F20+G20-H20</f>
-        <v>803411.33333333337</v>
+        <v>645010.67999999993</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>
@@ -1741,22 +1745,70 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
+      <c r="A21" s="11">
+        <v>1003483344</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="4">
+        <v>291817.5</v>
+      </c>
+      <c r="D21" s="5">
+        <v>41515.833333333328</v>
+      </c>
+      <c r="E21" s="13">
+        <v>56313</v>
+      </c>
+      <c r="F21" s="13">
+        <v>23345.4</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13">
+        <v>0</v>
+      </c>
+      <c r="I21" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="13">
+        <v>366300.93333333329</v>
+      </c>
+      <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="13">
+        <v>0</v>
+      </c>
+      <c r="N21" s="14">
+        <v>0</v>
+      </c>
+      <c r="O21" s="23"/>
+      <c r="P21" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
